--- a/URLCanonique/ig/StructureDefinition-FRLMReasonForReferral.xlsx
+++ b/URLCanonique/ig/StructureDefinition-FRLMReasonForReferral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:39:54+00:00</t>
+    <t>2026-09-30T08:56:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,7 +375,7 @@
 </t>
   </si>
   <si>
-    <t>Simple observation</t>
+    <t>Observation</t>
   </si>
   <si>
     <t>FRLMReasonForReferral.entry.problemes</t>
